--- a/cases/brightwater-acquisition/docs/04_data_room_index.xlsx
+++ b/cases/brightwater-acquisition/docs/04_data_room_index.xlsx
@@ -931,7 +931,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lease of Floor 3, 26 Clerkenwell Road</t>
+          <t>Lease of Floor 3, 26 Copperfield Yard</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
